--- a/تهیه کارنامه نواحی.xlsx
+++ b/تهیه کارنامه نواحی.xlsx
@@ -6281,7 +6281,7 @@
     <row r="70" ht="20" customHeight="1" s="12">
       <c r="A70" s="102" t="inlineStr">
         <is>
-          <t>۲. نکته محاسباتی شاخص ۱: حدانتظار سواد رسانه حضوری (ضریب ۳۱×) حاصل جمع نشست‌های حضوری (شیت سوادرسانه حضوری) و کارگاه‌های توانمندسازی (شیت توانمندسازی گردان) در فایل اکسل ماهانه کارمندان است.</t>
+          <t>۲. مبنای محاسبه شاخص‌ها: ملاک محاسبه عملکرد در شیت‌های حضوری، توانمندسازی، مجازی و خلاقانه، «مجموع تعداد نفرات / مخاطبان» ثبت‌شده در ستون تعداد نفرات کلاس‌ها است (در شاخص ۱: مجموع نفرات شیت‌های حضوری و توانمندسازی گردان).</t>
         </is>
       </c>
     </row>

--- a/تهیه کارنامه نواحی.xlsx
+++ b/تهیه کارنامه نواحی.xlsx
@@ -696,7 +696,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -1024,6 +1024,20 @@
     <xf numFmtId="3" fontId="26" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1196,7 +1210,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -1608,43 +1621,43 @@
           <t>🏢 پوشش تشکیلاتی استان</t>
         </is>
       </c>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
+      <c r="C4" s="115" t="n"/>
+      <c r="D4" s="116" t="n"/>
       <c r="E4" s="17" t="inlineStr">
         <is>
           <t>📊 میانگین نمره عملکرد استان</t>
         </is>
       </c>
-      <c r="F4" s="18" t="n"/>
-      <c r="G4" s="18" t="n"/>
-      <c r="H4" s="18" t="n"/>
+      <c r="F4" s="117" t="n"/>
+      <c r="G4" s="117" t="n"/>
+      <c r="H4" s="118" t="n"/>
       <c r="I4" s="19" t="inlineStr">
         <is>
           <t>🏆 پیشتاز عملکرد استان (رتبه ۱)</t>
         </is>
       </c>
-      <c r="J4" s="20" t="n"/>
-      <c r="K4" s="20" t="n"/>
-      <c r="L4" s="20" t="n"/>
+      <c r="J4" s="119" t="n"/>
+      <c r="K4" s="119" t="n"/>
+      <c r="L4" s="120" t="n"/>
       <c r="M4" s="21" t="inlineStr">
         <is>
           <t>📥 وضعیت دریافت گزارش ماهانه</t>
         </is>
       </c>
-      <c r="N4" s="22" t="n"/>
-      <c r="O4" s="22" t="n"/>
-      <c r="P4" s="22" t="n"/>
+      <c r="N4" s="121" t="n"/>
+      <c r="O4" s="121" t="n"/>
+      <c r="P4" s="122" t="n"/>
       <c r="Q4" s="23" t="inlineStr">
         <is>
           <t>🎯 تفکیک سطوح کیفی عملکرد نواحی</t>
         </is>
       </c>
-      <c r="R4" s="24" t="n"/>
-      <c r="S4" s="24" t="n"/>
-      <c r="T4" s="24" t="n"/>
-      <c r="U4" s="24" t="n"/>
-      <c r="V4" s="24" t="n"/>
-      <c r="W4" s="24" t="n"/>
+      <c r="R4" s="123" t="n"/>
+      <c r="S4" s="123" t="n"/>
+      <c r="T4" s="123" t="n"/>
+      <c r="U4" s="123" t="n"/>
+      <c r="V4" s="123" t="n"/>
+      <c r="W4" s="124" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1" s="12">
       <c r="B5" s="25" t="inlineStr">
@@ -1652,78 +1665,78 @@
           <t>۳۲ ناحیه | ۲۲۹ حوزه مقاومت</t>
         </is>
       </c>
-      <c r="C5" s="26" t="n"/>
-      <c r="D5" s="26" t="n"/>
+      <c r="C5" s="125" t="n"/>
+      <c r="D5" s="126" t="n"/>
       <c r="E5" s="27">
         <f>IFERROR(AVERAGE(T31:T62), 0)</f>
         <v/>
       </c>
-      <c r="F5" s="28" t="n"/>
-      <c r="G5" s="28" t="n"/>
-      <c r="H5" s="28" t="n"/>
+      <c r="F5" s="125" t="n"/>
+      <c r="G5" s="125" t="n"/>
+      <c r="H5" s="126" t="n"/>
       <c r="I5" s="29">
         <f>IF(MAX(T31:T62)&gt;0, INDEX(B31:B62, MATCH(MAX(T31:T62), T31:T62, 0)), "در انتظار ثبت داده")</f>
         <v/>
       </c>
-      <c r="J5" s="30" t="n"/>
-      <c r="K5" s="30" t="n"/>
-      <c r="L5" s="30" t="n"/>
+      <c r="J5" s="125" t="n"/>
+      <c r="K5" s="125" t="n"/>
+      <c r="L5" s="126" t="n"/>
       <c r="M5" s="31">
         <f>COUNTIF(W31:W62, "ثبت شده") &amp; " از ۳۲ ناحیه"</f>
         <v/>
       </c>
-      <c r="N5" s="32" t="n"/>
-      <c r="O5" s="32" t="n"/>
-      <c r="P5" s="32" t="n"/>
+      <c r="N5" s="125" t="n"/>
+      <c r="O5" s="125" t="n"/>
+      <c r="P5" s="126" t="n"/>
       <c r="Q5" s="33">
         <f>"عالی: " &amp; COUNTIF(V31:V62, "عالی*") &amp; " | خوب: " &amp; COUNTIF(V31:V62, "خوب*") &amp; " | متوسط: " &amp; COUNTIF(V31:V62, "متوسط*") &amp; " | ضعیف: " &amp; COUNTIF(V31:V62, "ضعیف*")</f>
         <v/>
       </c>
-      <c r="R5" s="34" t="n"/>
-      <c r="S5" s="34" t="n"/>
-      <c r="T5" s="34" t="n"/>
-      <c r="U5" s="34" t="n"/>
-      <c r="V5" s="34" t="n"/>
-      <c r="W5" s="34" t="n"/>
+      <c r="R5" s="125" t="n"/>
+      <c r="S5" s="125" t="n"/>
+      <c r="T5" s="125" t="n"/>
+      <c r="U5" s="125" t="n"/>
+      <c r="V5" s="125" t="n"/>
+      <c r="W5" s="126" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="12">
       <c r="B6" s="35">
         <f>"مجموع مدرسان هدف: " &amp; TEXT(SUM('پایگاه داده حد انتظار'!$H$2:$H$33),"#,##0") &amp; " نفر"</f>
         <v/>
       </c>
-      <c r="C6" s="26" t="n"/>
-      <c r="D6" s="26" t="n"/>
+      <c r="C6" s="125" t="n"/>
+      <c r="D6" s="126" t="n"/>
       <c r="E6" s="36">
         <f>IF(E5&gt;=1,"تحقق ۱۰۰٪ اهداف استانی",IF(E5&gt;=0.75,"عملکرد بسیار مطلوب",IF(E5&gt;=0.5,"عملکرد متوسط","نیازمند مداخله و پیگیری")))</f>
         <v/>
       </c>
-      <c r="F6" s="28" t="n"/>
-      <c r="G6" s="28" t="n"/>
-      <c r="H6" s="28" t="n"/>
+      <c r="F6" s="125" t="n"/>
+      <c r="G6" s="125" t="n"/>
+      <c r="H6" s="126" t="n"/>
       <c r="I6" s="37">
         <f>IF(MAX(T31:T62)&gt;0, "نمره تحقق: " &amp; TEXT(MAX(T31:T62), "0.0%"), "-")</f>
         <v/>
       </c>
-      <c r="J6" s="30" t="n"/>
-      <c r="K6" s="30" t="n"/>
-      <c r="L6" s="30" t="n"/>
+      <c r="J6" s="125" t="n"/>
+      <c r="K6" s="125" t="n"/>
+      <c r="L6" s="126" t="n"/>
       <c r="M6" s="38">
         <f>"نرخ مشارکت: " &amp; TEXT(COUNTIF(W31:W62, "ثبت شده")/32, "0.0%")</f>
         <v/>
       </c>
-      <c r="N6" s="32" t="n"/>
-      <c r="O6" s="32" t="n"/>
-      <c r="P6" s="32" t="n"/>
+      <c r="N6" s="125" t="n"/>
+      <c r="O6" s="125" t="n"/>
+      <c r="P6" s="126" t="n"/>
       <c r="Q6" s="39">
         <f>"نواحی فاقد گزارش: " &amp; COUNTIF(W31:W62, "فاقد گزارش") &amp; " ناحیه"</f>
         <v/>
       </c>
-      <c r="R6" s="34" t="n"/>
-      <c r="S6" s="34" t="n"/>
-      <c r="T6" s="34" t="n"/>
-      <c r="U6" s="34" t="n"/>
-      <c r="V6" s="34" t="n"/>
-      <c r="W6" s="34" t="n"/>
+      <c r="R6" s="125" t="n"/>
+      <c r="S6" s="125" t="n"/>
+      <c r="T6" s="125" t="n"/>
+      <c r="U6" s="125" t="n"/>
+      <c r="V6" s="125" t="n"/>
+      <c r="W6" s="126" t="n"/>
     </row>
     <row r="7" ht="8" customHeight="1" s="12"/>
     <row r="8" ht="8" customHeight="1" s="12"/>
@@ -2693,43 +2706,43 @@
           <t>مشخصات کلی ناحیه</t>
         </is>
       </c>
-      <c r="B29" s="67" t="n"/>
-      <c r="C29" s="67" t="n"/>
+      <c r="B29" s="127" t="n"/>
+      <c r="C29" s="128" t="n"/>
       <c r="D29" s="68" t="inlineStr">
         <is>
           <t>۱. حضوری و توانمندسازی (۳۱×)</t>
         </is>
       </c>
-      <c r="E29" s="69" t="n"/>
-      <c r="F29" s="69" t="n"/>
+      <c r="E29" s="127" t="n"/>
+      <c r="F29" s="128" t="n"/>
       <c r="G29" s="70" t="inlineStr">
         <is>
           <t>۲. مجازی و لایو (۲۱۷×)</t>
         </is>
       </c>
-      <c r="H29" s="71" t="n"/>
-      <c r="I29" s="71" t="n"/>
+      <c r="H29" s="127" t="n"/>
+      <c r="I29" s="128" t="n"/>
       <c r="J29" s="72" t="inlineStr">
         <is>
           <t>۳. اقدامات خلاقانه (۶۲×)</t>
         </is>
       </c>
-      <c r="K29" s="73" t="n"/>
-      <c r="L29" s="73" t="n"/>
+      <c r="K29" s="127" t="n"/>
+      <c r="L29" s="128" t="n"/>
       <c r="M29" s="74" t="inlineStr">
         <is>
           <t>۴. تولیدات رسانه‌ای (۳×)</t>
         </is>
       </c>
-      <c r="N29" s="75" t="n"/>
-      <c r="O29" s="75" t="n"/>
+      <c r="N29" s="127" t="n"/>
+      <c r="O29" s="128" t="n"/>
       <c r="P29" s="76" t="inlineStr">
         <is>
           <t>۵. نشست انجمن (۱×)</t>
         </is>
       </c>
-      <c r="Q29" s="77" t="n"/>
-      <c r="R29" s="77" t="n"/>
+      <c r="Q29" s="127" t="n"/>
+      <c r="R29" s="128" t="n"/>
       <c r="S29" s="78" t="inlineStr">
         <is>
           <t>۶. اعضا</t>
@@ -2740,9 +2753,9 @@
           <t>ارزیابی نهایی و رتبه‌بندی استانی</t>
         </is>
       </c>
-      <c r="U29" s="80" t="n"/>
-      <c r="V29" s="80" t="n"/>
-      <c r="W29" s="80" t="n"/>
+      <c r="U29" s="127" t="n"/>
+      <c r="V29" s="127" t="n"/>
+      <c r="W29" s="128" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1" s="12">
       <c r="A30" s="41" t="inlineStr">
@@ -6297,14 +6310,23 @@
         <f>HYPERLINK("#'کارنامه هوشمند'!A1", "📋 ورود به شیت صدور کارنامه هوشمند نواحی ↗")</f>
         <v/>
       </c>
+      <c r="C73" s="127" t="n"/>
+      <c r="D73" s="127" t="n"/>
+      <c r="E73" s="128" t="n"/>
       <c r="F73" s="104">
         <f>HYPERLINK("#'گزارش عملکرد ماهانه'!A1", "✏️ ورود به شیت ثبت عملکرد ماهانه نواحی ↗")</f>
         <v/>
       </c>
+      <c r="G73" s="127" t="n"/>
+      <c r="H73" s="127" t="n"/>
+      <c r="I73" s="128" t="n"/>
       <c r="J73" s="105">
         <f>HYPERLINK("#'پایگاه داده حد انتظار'!A1", "⚙️ ورود به پایگاه داده و حدانتظار حوزه‌ها ↗")</f>
         <v/>
       </c>
+      <c r="K73" s="127" t="n"/>
+      <c r="L73" s="127" t="n"/>
+      <c r="M73" s="128" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="36">
@@ -6756,11 +6778,21 @@
           <t>امام رضا(ع)</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="9" t="n"/>
-      <c r="F4" s="9" t="n"/>
+      <c r="B4" s="9" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -6768,11 +6800,21 @@
           <t>امام صادق(ع)</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n"/>
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="9" t="n"/>
-      <c r="F5" s="9" t="n"/>
+      <c r="B5" s="9" t="n">
+        <v>4189</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -6780,11 +6822,21 @@
           <t>امام علی(ع)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n"/>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="9" t="n"/>
-      <c r="E6" s="9" t="n"/>
-      <c r="F6" s="9" t="n"/>
+      <c r="B6" s="9" t="n">
+        <v>815</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -6792,11 +6844,21 @@
           <t>اردستان</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="9" t="n"/>
+      <c r="B7" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -6804,11 +6866,21 @@
           <t>برخوار</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>4396</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -6840,11 +6912,21 @@
           <t>جرقویه</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
+      <c r="B11" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -6876,11 +6958,21 @@
           <t>خوانسار</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
+      <c r="B14" s="9" t="n">
+        <v>156</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>1634</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -6900,11 +6992,21 @@
           <t>درچه</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
+      <c r="B16" s="9" t="n">
+        <v>2299</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -6948,11 +7050,21 @@
           <t>شهرضا</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="n"/>
+      <c r="B20" s="9" t="n">
+        <v>213</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>3366</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
@@ -6972,11 +7084,21 @@
           <t>فریدون شهر</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
+      <c r="B22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
@@ -6984,11 +7106,21 @@
           <t>فلاورجان</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
+      <c r="B23" s="9" t="n">
+        <v>1583</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>11348</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -6996,11 +7128,21 @@
           <t>کاشان</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
+      <c r="B24" s="9" t="n">
+        <v>455</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>136</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
@@ -7008,11 +7150,21 @@
           <t>کوهپایه</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
+      <c r="B25" s="9" t="n">
+        <v>264</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>502</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
@@ -7032,11 +7184,21 @@
           <t>لنجان</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="9" t="n"/>
+      <c r="B27" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
@@ -7080,11 +7242,21 @@
           <t>نطنز</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
+      <c r="B31" s="9" t="n">
+        <v>1002</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>187</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">

--- a/تهیه کارنامه نواحی.xlsx
+++ b/تهیه کارنامه نواحی.xlsx
@@ -188,7 +188,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill/>
     </fill>
@@ -339,8 +339,14 @@
         <bgColor rgb="00EAECEE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0027AE60"/>
+        <bgColor rgb="0027AE60"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="38">
+  <borders count="40">
     <border/>
     <border>
       <left style="thin">
@@ -692,11 +698,39 @@
         <color rgb="00BDC3C7"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="001B365D"/>
+      </left>
+      <right style="medium">
+        <color rgb="001B365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E8449"/>
+      </left>
+      <right style="medium">
+        <color rgb="001E8449"/>
+      </right>
+      <top style="medium">
+        <color rgb="001E8449"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001E8449"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -1038,6 +1072,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1608,9 +1651,14 @@
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" s="12">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="129" t="inlineStr">
         <is>
           <t>سال ارزیابی: ۱۴۰۵ | مبنای سنجش: شاخص‌های ابلاغی به ازای هر حوزه مقاومت | پایش برخط و خودکار متصل به گزارش عملکرد ماهانه</t>
+        </is>
+      </c>
+      <c r="V2" s="130" t="inlineStr">
+        <is>
+          <t>📸 خروجی تصویر داشبورد</t>
         </is>
       </c>
     </row>
@@ -6329,14 +6377,16 @@
       <c r="M73" s="128" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="37">
     <mergeCell ref="A68:W68"/>
+    <mergeCell ref="V2:W2"/>
     <mergeCell ref="B9:K9"/>
     <mergeCell ref="I4:L4"/>
     <mergeCell ref="S29"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="M4:P4"/>
     <mergeCell ref="A70:W70"/>
+    <mergeCell ref="A2:U2"/>
     <mergeCell ref="A69:W69"/>
     <mergeCell ref="M20:W20"/>
     <mergeCell ref="F73:I73"/>
@@ -6353,7 +6403,6 @@
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="E4:H4"/>
     <mergeCell ref="B4:D4"/>
-    <mergeCell ref="A2:W2"/>
     <mergeCell ref="A71:W71"/>
     <mergeCell ref="Q5:W5"/>
     <mergeCell ref="J29:L29"/>
@@ -6503,8 +6552,11 @@
           <t>آران و بیدگل</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n"/>
-      <c r="E2" s="6" t="n"/>
+      <c r="D2" s="131" t="inlineStr">
+        <is>
+          <t>📸 دریافت تصویر کارنامه (PNG)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="B3" s="6" t="n"/>
@@ -6695,6 +6747,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D2:E2"/>
+  </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="C2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'پایگاه داده حد انتظار'!$A$2:$A$33</formula1>

--- a/تهیه کارنامه نواحی.xlsx
+++ b/تهیه کارنامه نواحی.xlsx
@@ -19,7 +19,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="31">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -187,8 +187,26 @@
       <color rgb="001B365D"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="IRANSans"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="IRANSans"/>
+      <b val="1"/>
+      <color rgb="00843B62"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="IRANSans"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="27">
+  <fills count="29">
     <fill>
       <patternFill/>
     </fill>
@@ -345,8 +363,20 @@
         <bgColor rgb="0027AE60"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF1F5"/>
+        <bgColor rgb="00EBF1F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="40">
+  <borders count="45">
     <border/>
     <border>
       <left style="thin">
@@ -726,11 +756,54 @@
         <color rgb="001E8449"/>
       </bottom>
     </border>
+    <border>
+      <top style="medium">
+        <color rgb="001E8449"/>
+      </top>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="001E8449"/>
+      </right>
+      <top style="medium">
+        <color rgb="001E8449"/>
+      </top>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="001E8449"/>
+      </right>
+      <top style="medium">
+        <color rgb="001E8449"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001E8449"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="001B365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="001B365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -1081,6 +1154,20 @@
     <xf numFmtId="0" fontId="16" fillId="10" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1651,16 +1738,16 @@
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" s="12">
-      <c r="A2" s="129" t="inlineStr">
-        <is>
-          <t>سال ارزیابی: ۱۴۰۵ | مبنای سنجش: شاخص‌های ابلاغی به ازای هر حوزه مقاومت | پایش برخط و خودکار متصل به گزارش عملکرد ماهانه</t>
-        </is>
+      <c r="A2" s="129">
+        <f>"سال ارزیابی: ۱۴۰۵ | دوره ارزیابی: " &amp; 'کارنامه هوشمند'!C3 &amp; " ماه | مبنای سنجش: شاخص‌های ابلاغی به ازای هر حوزه مقاومت | پایش برخط و خودکار متصل به گزارش عملکرد ماهانه"</f>
+        <v/>
       </c>
       <c r="V2" s="130" t="inlineStr">
         <is>
           <t>📸 خروجی تصویر داشبورد</t>
         </is>
       </c>
+      <c r="W2" s="132" t="n"/>
     </row>
     <row r="3" ht="10" customHeight="1" s="12"/>
     <row r="4" ht="22" customHeight="1" s="12">
@@ -6557,12 +6644,24 @@
           <t>📸 دریافت تصویر کارنامه (PNG)</t>
         </is>
       </c>
+      <c r="E2" s="133" t="n"/>
     </row>
     <row r="3">
-      <c r="B3" s="6" t="n"/>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
+      <c r="B3" s="134" t="inlineStr">
+        <is>
+          <t>ماه دوره ارزیابی:</t>
+        </is>
+      </c>
+      <c r="C3" s="135" t="inlineStr">
+        <is>
+          <t>شهریور</t>
+        </is>
+      </c>
+      <c r="D3" s="136">
+        <f>"کارنامه ارزیابی عملکرد ماه " &amp; C3 &amp; " ۱۴۰۵"</f>
+        <v/>
+      </c>
+      <c r="E3" s="137" t="n"/>
     </row>
     <row r="4">
       <c r="B4" s="7" t="inlineStr">
@@ -6747,12 +6846,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
     <mergeCell ref="D2:E2"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="C2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'پایگاه داده حد انتظار'!$A$2:$A$33</formula1>
+    </dataValidation>
+    <dataValidation sqref="C3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"فروردین,اردیبهشت,خرداد,تیر,مرداد,شهریور,مهر,آبان,آذر,دی,بهمن,اسفند"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6768,7 +6871,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -6801,6 +6904,15 @@
         <is>
           <t>نشست انجمن</t>
         </is>
+      </c>
+      <c r="G1" s="138" t="inlineStr">
+        <is>
+          <t>دوره ارزیابی:</t>
+        </is>
+      </c>
+      <c r="H1" s="139">
+        <f>'کارنامه هوشمند'!C3</f>
+        <v/>
       </c>
     </row>
     <row r="2">

--- a/تهیه کارنامه نواحی.xlsx
+++ b/تهیه کارنامه نواحی.xlsx
@@ -1739,7 +1739,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" s="12">
       <c r="A2" s="129">
-        <f>"سال ارزیابی: ۱۴۰۵ | دوره ارزیابی: " &amp; 'کارنامه هوشمند'!C3 &amp; " ماه | مبنای سنجش: شاخص‌های ابلاغی به ازای هر حوزه مقاومت | پایش برخط و خودکار متصل به گزارش عملکرد ماهانه"</f>
+        <f>"سال ارزیابی: " &amp; 'کارنامه هوشمند'!E3 &amp; " | دوره ارزیابی: ماه " &amp; 'کارنامه هوشمند'!C3 &amp; " | مبنای سنجش: شاخص‌های ابلاغی به ازای هر حوزه مقاومت | پایش برخط و خودکار متصل به گزارش عملکرد ماهانه"</f>
         <v/>
       </c>
       <c r="V2" s="130" t="inlineStr">
@@ -6616,7 +6616,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="25.13" customWidth="1" style="12" min="2" max="5"/>
@@ -6649,19 +6649,24 @@
     <row r="3">
       <c r="B3" s="134" t="inlineStr">
         <is>
-          <t>ماه دوره ارزیابی:</t>
+          <t>ماه ارزیابی:</t>
         </is>
       </c>
       <c r="C3" s="135" t="inlineStr">
         <is>
-          <t>شهریور</t>
-        </is>
-      </c>
-      <c r="D3" s="136">
-        <f>"کارنامه ارزیابی عملکرد ماه " &amp; C3 &amp; " ۱۴۰۵"</f>
-        <v/>
-      </c>
-      <c r="E3" s="137" t="n"/>
+          <t>مرداد</t>
+        </is>
+      </c>
+      <c r="D3" s="134" t="inlineStr">
+        <is>
+          <t>سال ارزیابی:</t>
+        </is>
+      </c>
+      <c r="E3" s="135" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" s="7" t="inlineStr">
@@ -6846,13 +6851,15 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
+  <mergeCells count="1">
     <mergeCell ref="D2:E2"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="C2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'پایگاه داده حد انتظار'!$A$2:$A$33</formula1>
+    </dataValidation>
+    <dataValidation sqref="C3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"فروردین,اردیبهشت,خرداد,تیر,مرداد,شهریور,مهر,آبان,آذر,دی,بهمن,اسفند"</formula1>
     </dataValidation>
     <dataValidation sqref="C3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"فروردین,اردیبهشت,خرداد,تیر,مرداد,شهریور,مهر,آبان,آذر,دی,بهمن,اسفند"</formula1>
@@ -6911,7 +6918,7 @@
         </is>
       </c>
       <c r="H1" s="139">
-        <f>'کارنامه هوشمند'!C3</f>
+        <f>'کارنامه هوشمند'!C3 &amp; " " &amp; 'کارنامه هوشمند'!E3</f>
         <v/>
       </c>
     </row>

--- a/تهیه کارنامه نواحی.xlsx
+++ b/تهیه کارنامه نواحی.xlsx
@@ -803,7 +803,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -1168,6 +1168,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2990,7 +2993,7 @@
       </c>
       <c r="T30" s="41" t="inlineStr">
         <is>
-          <t>نمره کل عملکرد</t>
+          <t>نمره کل عملکرد (۷۰-۱۰۰)</t>
         </is>
       </c>
       <c r="U30" s="41" t="inlineStr">
@@ -3000,7 +3003,7 @@
       </c>
       <c r="V30" s="41" t="inlineStr">
         <is>
-          <t>سطح ارزیابی</t>
+          <t>سطح ارزیابی (۳ سطح)</t>
         </is>
       </c>
       <c r="W30" s="41" t="inlineStr">
@@ -3087,15 +3090,15 @@
         <v/>
       </c>
       <c r="T31" s="83">
-        <f>AVERAGE(F31, I31, L31, O31, R31)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F31 + 0.3*I31) + MIN(0.5, 0.5*L31 + MAX(0, 0.1*F31 + 0.3*I31 - 0.4)) + MIN(0.1, 0.1*O31)), 1)</f>
         <v/>
       </c>
       <c r="U31" s="58">
-        <f>IF(T31&gt;0, RANK(T31, $T$31:$T$62), "-")</f>
+        <f>IF(T31&gt;70, RANK(T31, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V31" s="60">
-        <f>IF(W31="فاقد گزارش", "ثبت نشده", IF(T31&gt;=1, "عالی (۱۰۰٪+)", IF(T31&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T31&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T31&lt;=70, "ضعیف", IF(T31&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W31" s="60">
@@ -3181,15 +3184,15 @@
         <v/>
       </c>
       <c r="T32" s="86">
-        <f>AVERAGE(F32, I32, L32, O32, R32)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F32 + 0.3*I32) + MIN(0.5, 0.5*L32 + MAX(0, 0.1*F32 + 0.3*I32 - 0.4)) + MIN(0.1, 0.1*O32)), 1)</f>
         <v/>
       </c>
       <c r="U32" s="62">
-        <f>IF(T32&gt;0, RANK(T32, $T$31:$T$62), "-")</f>
+        <f>IF(T32&gt;70, RANK(T32, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V32" s="64">
-        <f>IF(W32="فاقد گزارش", "ثبت نشده", IF(T32&gt;=1, "عالی (۱۰۰٪+)", IF(T32&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T32&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T32&lt;=70, "ضعیف", IF(T32&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W32" s="64">
@@ -3275,15 +3278,15 @@
         <v/>
       </c>
       <c r="T33" s="83">
-        <f>AVERAGE(F33, I33, L33, O33, R33)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F33 + 0.3*I33) + MIN(0.5, 0.5*L33 + MAX(0, 0.1*F33 + 0.3*I33 - 0.4)) + MIN(0.1, 0.1*O33)), 1)</f>
         <v/>
       </c>
       <c r="U33" s="58">
-        <f>IF(T33&gt;0, RANK(T33, $T$31:$T$62), "-")</f>
+        <f>IF(T33&gt;70, RANK(T33, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V33" s="60">
-        <f>IF(W33="فاقد گزارش", "ثبت نشده", IF(T33&gt;=1, "عالی (۱۰۰٪+)", IF(T33&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T33&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T33&lt;=70, "ضعیف", IF(T33&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W33" s="60">
@@ -3369,15 +3372,15 @@
         <v/>
       </c>
       <c r="T34" s="86">
-        <f>AVERAGE(F34, I34, L34, O34, R34)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F34 + 0.3*I34) + MIN(0.5, 0.5*L34 + MAX(0, 0.1*F34 + 0.3*I34 - 0.4)) + MIN(0.1, 0.1*O34)), 1)</f>
         <v/>
       </c>
       <c r="U34" s="62">
-        <f>IF(T34&gt;0, RANK(T34, $T$31:$T$62), "-")</f>
+        <f>IF(T34&gt;70, RANK(T34, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V34" s="64">
-        <f>IF(W34="فاقد گزارش", "ثبت نشده", IF(T34&gt;=1, "عالی (۱۰۰٪+)", IF(T34&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T34&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T34&lt;=70, "ضعیف", IF(T34&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W34" s="64">
@@ -3463,15 +3466,15 @@
         <v/>
       </c>
       <c r="T35" s="83">
-        <f>AVERAGE(F35, I35, L35, O35, R35)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F35 + 0.3*I35) + MIN(0.5, 0.5*L35 + MAX(0, 0.1*F35 + 0.3*I35 - 0.4)) + MIN(0.1, 0.1*O35)), 1)</f>
         <v/>
       </c>
       <c r="U35" s="58">
-        <f>IF(T35&gt;0, RANK(T35, $T$31:$T$62), "-")</f>
+        <f>IF(T35&gt;70, RANK(T35, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V35" s="60">
-        <f>IF(W35="فاقد گزارش", "ثبت نشده", IF(T35&gt;=1, "عالی (۱۰۰٪+)", IF(T35&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T35&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T35&lt;=70, "ضعیف", IF(T35&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W35" s="60">
@@ -3557,15 +3560,15 @@
         <v/>
       </c>
       <c r="T36" s="86">
-        <f>AVERAGE(F36, I36, L36, O36, R36)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F36 + 0.3*I36) + MIN(0.5, 0.5*L36 + MAX(0, 0.1*F36 + 0.3*I36 - 0.4)) + MIN(0.1, 0.1*O36)), 1)</f>
         <v/>
       </c>
       <c r="U36" s="62">
-        <f>IF(T36&gt;0, RANK(T36, $T$31:$T$62), "-")</f>
+        <f>IF(T36&gt;70, RANK(T36, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V36" s="64">
-        <f>IF(W36="فاقد گزارش", "ثبت نشده", IF(T36&gt;=1, "عالی (۱۰۰٪+)", IF(T36&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T36&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T36&lt;=70, "ضعیف", IF(T36&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W36" s="64">
@@ -3651,15 +3654,15 @@
         <v/>
       </c>
       <c r="T37" s="83">
-        <f>AVERAGE(F37, I37, L37, O37, R37)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F37 + 0.3*I37) + MIN(0.5, 0.5*L37 + MAX(0, 0.1*F37 + 0.3*I37 - 0.4)) + MIN(0.1, 0.1*O37)), 1)</f>
         <v/>
       </c>
       <c r="U37" s="58">
-        <f>IF(T37&gt;0, RANK(T37, $T$31:$T$62), "-")</f>
+        <f>IF(T37&gt;70, RANK(T37, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V37" s="60">
-        <f>IF(W37="فاقد گزارش", "ثبت نشده", IF(T37&gt;=1, "عالی (۱۰۰٪+)", IF(T37&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T37&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T37&lt;=70, "ضعیف", IF(T37&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W37" s="60">
@@ -3745,15 +3748,15 @@
         <v/>
       </c>
       <c r="T38" s="86">
-        <f>AVERAGE(F38, I38, L38, O38, R38)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F38 + 0.3*I38) + MIN(0.5, 0.5*L38 + MAX(0, 0.1*F38 + 0.3*I38 - 0.4)) + MIN(0.1, 0.1*O38)), 1)</f>
         <v/>
       </c>
       <c r="U38" s="62">
-        <f>IF(T38&gt;0, RANK(T38, $T$31:$T$62), "-")</f>
+        <f>IF(T38&gt;70, RANK(T38, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V38" s="64">
-        <f>IF(W38="فاقد گزارش", "ثبت نشده", IF(T38&gt;=1, "عالی (۱۰۰٪+)", IF(T38&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T38&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T38&lt;=70, "ضعیف", IF(T38&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W38" s="64">
@@ -3839,15 +3842,15 @@
         <v/>
       </c>
       <c r="T39" s="83">
-        <f>AVERAGE(F39, I39, L39, O39, R39)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F39 + 0.3*I39) + MIN(0.5, 0.5*L39 + MAX(0, 0.1*F39 + 0.3*I39 - 0.4)) + MIN(0.1, 0.1*O39)), 1)</f>
         <v/>
       </c>
       <c r="U39" s="58">
-        <f>IF(T39&gt;0, RANK(T39, $T$31:$T$62), "-")</f>
+        <f>IF(T39&gt;70, RANK(T39, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V39" s="60">
-        <f>IF(W39="فاقد گزارش", "ثبت نشده", IF(T39&gt;=1, "عالی (۱۰۰٪+)", IF(T39&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T39&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T39&lt;=70, "ضعیف", IF(T39&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W39" s="60">
@@ -3933,15 +3936,15 @@
         <v/>
       </c>
       <c r="T40" s="86">
-        <f>AVERAGE(F40, I40, L40, O40, R40)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F40 + 0.3*I40) + MIN(0.5, 0.5*L40 + MAX(0, 0.1*F40 + 0.3*I40 - 0.4)) + MIN(0.1, 0.1*O40)), 1)</f>
         <v/>
       </c>
       <c r="U40" s="62">
-        <f>IF(T40&gt;0, RANK(T40, $T$31:$T$62), "-")</f>
+        <f>IF(T40&gt;70, RANK(T40, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V40" s="64">
-        <f>IF(W40="فاقد گزارش", "ثبت نشده", IF(T40&gt;=1, "عالی (۱۰۰٪+)", IF(T40&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T40&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T40&lt;=70, "ضعیف", IF(T40&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W40" s="64">
@@ -4027,15 +4030,15 @@
         <v/>
       </c>
       <c r="T41" s="83">
-        <f>AVERAGE(F41, I41, L41, O41, R41)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F41 + 0.3*I41) + MIN(0.5, 0.5*L41 + MAX(0, 0.1*F41 + 0.3*I41 - 0.4)) + MIN(0.1, 0.1*O41)), 1)</f>
         <v/>
       </c>
       <c r="U41" s="58">
-        <f>IF(T41&gt;0, RANK(T41, $T$31:$T$62), "-")</f>
+        <f>IF(T41&gt;70, RANK(T41, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V41" s="60">
-        <f>IF(W41="فاقد گزارش", "ثبت نشده", IF(T41&gt;=1, "عالی (۱۰۰٪+)", IF(T41&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T41&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T41&lt;=70, "ضعیف", IF(T41&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W41" s="60">
@@ -4121,15 +4124,15 @@
         <v/>
       </c>
       <c r="T42" s="86">
-        <f>AVERAGE(F42, I42, L42, O42, R42)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F42 + 0.3*I42) + MIN(0.5, 0.5*L42 + MAX(0, 0.1*F42 + 0.3*I42 - 0.4)) + MIN(0.1, 0.1*O42)), 1)</f>
         <v/>
       </c>
       <c r="U42" s="62">
-        <f>IF(T42&gt;0, RANK(T42, $T$31:$T$62), "-")</f>
+        <f>IF(T42&gt;70, RANK(T42, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V42" s="64">
-        <f>IF(W42="فاقد گزارش", "ثبت نشده", IF(T42&gt;=1, "عالی (۱۰۰٪+)", IF(T42&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T42&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T42&lt;=70, "ضعیف", IF(T42&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W42" s="64">
@@ -4215,15 +4218,15 @@
         <v/>
       </c>
       <c r="T43" s="83">
-        <f>AVERAGE(F43, I43, L43, O43, R43)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F43 + 0.3*I43) + MIN(0.5, 0.5*L43 + MAX(0, 0.1*F43 + 0.3*I43 - 0.4)) + MIN(0.1, 0.1*O43)), 1)</f>
         <v/>
       </c>
       <c r="U43" s="58">
-        <f>IF(T43&gt;0, RANK(T43, $T$31:$T$62), "-")</f>
+        <f>IF(T43&gt;70, RANK(T43, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V43" s="60">
-        <f>IF(W43="فاقد گزارش", "ثبت نشده", IF(T43&gt;=1, "عالی (۱۰۰٪+)", IF(T43&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T43&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T43&lt;=70, "ضعیف", IF(T43&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W43" s="60">
@@ -4309,15 +4312,15 @@
         <v/>
       </c>
       <c r="T44" s="86">
-        <f>AVERAGE(F44, I44, L44, O44, R44)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F44 + 0.3*I44) + MIN(0.5, 0.5*L44 + MAX(0, 0.1*F44 + 0.3*I44 - 0.4)) + MIN(0.1, 0.1*O44)), 1)</f>
         <v/>
       </c>
       <c r="U44" s="62">
-        <f>IF(T44&gt;0, RANK(T44, $T$31:$T$62), "-")</f>
+        <f>IF(T44&gt;70, RANK(T44, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V44" s="64">
-        <f>IF(W44="فاقد گزارش", "ثبت نشده", IF(T44&gt;=1, "عالی (۱۰۰٪+)", IF(T44&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T44&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T44&lt;=70, "ضعیف", IF(T44&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W44" s="64">
@@ -4403,15 +4406,15 @@
         <v/>
       </c>
       <c r="T45" s="83">
-        <f>AVERAGE(F45, I45, L45, O45, R45)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F45 + 0.3*I45) + MIN(0.5, 0.5*L45 + MAX(0, 0.1*F45 + 0.3*I45 - 0.4)) + MIN(0.1, 0.1*O45)), 1)</f>
         <v/>
       </c>
       <c r="U45" s="58">
-        <f>IF(T45&gt;0, RANK(T45, $T$31:$T$62), "-")</f>
+        <f>IF(T45&gt;70, RANK(T45, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V45" s="60">
-        <f>IF(W45="فاقد گزارش", "ثبت نشده", IF(T45&gt;=1, "عالی (۱۰۰٪+)", IF(T45&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T45&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T45&lt;=70, "ضعیف", IF(T45&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W45" s="60">
@@ -4497,15 +4500,15 @@
         <v/>
       </c>
       <c r="T46" s="86">
-        <f>AVERAGE(F46, I46, L46, O46, R46)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F46 + 0.3*I46) + MIN(0.5, 0.5*L46 + MAX(0, 0.1*F46 + 0.3*I46 - 0.4)) + MIN(0.1, 0.1*O46)), 1)</f>
         <v/>
       </c>
       <c r="U46" s="62">
-        <f>IF(T46&gt;0, RANK(T46, $T$31:$T$62), "-")</f>
+        <f>IF(T46&gt;70, RANK(T46, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V46" s="64">
-        <f>IF(W46="فاقد گزارش", "ثبت نشده", IF(T46&gt;=1, "عالی (۱۰۰٪+)", IF(T46&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T46&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T46&lt;=70, "ضعیف", IF(T46&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W46" s="64">
@@ -4591,15 +4594,15 @@
         <v/>
       </c>
       <c r="T47" s="83">
-        <f>AVERAGE(F47, I47, L47, O47, R47)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F47 + 0.3*I47) + MIN(0.5, 0.5*L47 + MAX(0, 0.1*F47 + 0.3*I47 - 0.4)) + MIN(0.1, 0.1*O47)), 1)</f>
         <v/>
       </c>
       <c r="U47" s="58">
-        <f>IF(T47&gt;0, RANK(T47, $T$31:$T$62), "-")</f>
+        <f>IF(T47&gt;70, RANK(T47, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V47" s="60">
-        <f>IF(W47="فاقد گزارش", "ثبت نشده", IF(T47&gt;=1, "عالی (۱۰۰٪+)", IF(T47&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T47&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T47&lt;=70, "ضعیف", IF(T47&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W47" s="60">
@@ -4685,15 +4688,15 @@
         <v/>
       </c>
       <c r="T48" s="86">
-        <f>AVERAGE(F48, I48, L48, O48, R48)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F48 + 0.3*I48) + MIN(0.5, 0.5*L48 + MAX(0, 0.1*F48 + 0.3*I48 - 0.4)) + MIN(0.1, 0.1*O48)), 1)</f>
         <v/>
       </c>
       <c r="U48" s="62">
-        <f>IF(T48&gt;0, RANK(T48, $T$31:$T$62), "-")</f>
+        <f>IF(T48&gt;70, RANK(T48, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V48" s="64">
-        <f>IF(W48="فاقد گزارش", "ثبت نشده", IF(T48&gt;=1, "عالی (۱۰۰٪+)", IF(T48&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T48&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T48&lt;=70, "ضعیف", IF(T48&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W48" s="64">
@@ -4779,15 +4782,15 @@
         <v/>
       </c>
       <c r="T49" s="83">
-        <f>AVERAGE(F49, I49, L49, O49, R49)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F49 + 0.3*I49) + MIN(0.5, 0.5*L49 + MAX(0, 0.1*F49 + 0.3*I49 - 0.4)) + MIN(0.1, 0.1*O49)), 1)</f>
         <v/>
       </c>
       <c r="U49" s="58">
-        <f>IF(T49&gt;0, RANK(T49, $T$31:$T$62), "-")</f>
+        <f>IF(T49&gt;70, RANK(T49, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V49" s="60">
-        <f>IF(W49="فاقد گزارش", "ثبت نشده", IF(T49&gt;=1, "عالی (۱۰۰٪+)", IF(T49&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T49&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T49&lt;=70, "ضعیف", IF(T49&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W49" s="60">
@@ -4873,15 +4876,15 @@
         <v/>
       </c>
       <c r="T50" s="86">
-        <f>AVERAGE(F50, I50, L50, O50, R50)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F50 + 0.3*I50) + MIN(0.5, 0.5*L50 + MAX(0, 0.1*F50 + 0.3*I50 - 0.4)) + MIN(0.1, 0.1*O50)), 1)</f>
         <v/>
       </c>
       <c r="U50" s="62">
-        <f>IF(T50&gt;0, RANK(T50, $T$31:$T$62), "-")</f>
+        <f>IF(T50&gt;70, RANK(T50, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V50" s="64">
-        <f>IF(W50="فاقد گزارش", "ثبت نشده", IF(T50&gt;=1, "عالی (۱۰۰٪+)", IF(T50&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T50&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T50&lt;=70, "ضعیف", IF(T50&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W50" s="64">
@@ -4967,15 +4970,15 @@
         <v/>
       </c>
       <c r="T51" s="83">
-        <f>AVERAGE(F51, I51, L51, O51, R51)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F51 + 0.3*I51) + MIN(0.5, 0.5*L51 + MAX(0, 0.1*F51 + 0.3*I51 - 0.4)) + MIN(0.1, 0.1*O51)), 1)</f>
         <v/>
       </c>
       <c r="U51" s="58">
-        <f>IF(T51&gt;0, RANK(T51, $T$31:$T$62), "-")</f>
+        <f>IF(T51&gt;70, RANK(T51, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V51" s="60">
-        <f>IF(W51="فاقد گزارش", "ثبت نشده", IF(T51&gt;=1, "عالی (۱۰۰٪+)", IF(T51&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T51&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T51&lt;=70, "ضعیف", IF(T51&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W51" s="60">
@@ -5061,15 +5064,15 @@
         <v/>
       </c>
       <c r="T52" s="86">
-        <f>AVERAGE(F52, I52, L52, O52, R52)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F52 + 0.3*I52) + MIN(0.5, 0.5*L52 + MAX(0, 0.1*F52 + 0.3*I52 - 0.4)) + MIN(0.1, 0.1*O52)), 1)</f>
         <v/>
       </c>
       <c r="U52" s="62">
-        <f>IF(T52&gt;0, RANK(T52, $T$31:$T$62), "-")</f>
+        <f>IF(T52&gt;70, RANK(T52, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V52" s="64">
-        <f>IF(W52="فاقد گزارش", "ثبت نشده", IF(T52&gt;=1, "عالی (۱۰۰٪+)", IF(T52&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T52&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T52&lt;=70, "ضعیف", IF(T52&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W52" s="64">
@@ -5155,15 +5158,15 @@
         <v/>
       </c>
       <c r="T53" s="83">
-        <f>AVERAGE(F53, I53, L53, O53, R53)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F53 + 0.3*I53) + MIN(0.5, 0.5*L53 + MAX(0, 0.1*F53 + 0.3*I53 - 0.4)) + MIN(0.1, 0.1*O53)), 1)</f>
         <v/>
       </c>
       <c r="U53" s="58">
-        <f>IF(T53&gt;0, RANK(T53, $T$31:$T$62), "-")</f>
+        <f>IF(T53&gt;70, RANK(T53, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V53" s="60">
-        <f>IF(W53="فاقد گزارش", "ثبت نشده", IF(T53&gt;=1, "عالی (۱۰۰٪+)", IF(T53&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T53&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T53&lt;=70, "ضعیف", IF(T53&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W53" s="60">
@@ -5249,15 +5252,15 @@
         <v/>
       </c>
       <c r="T54" s="86">
-        <f>AVERAGE(F54, I54, L54, O54, R54)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F54 + 0.3*I54) + MIN(0.5, 0.5*L54 + MAX(0, 0.1*F54 + 0.3*I54 - 0.4)) + MIN(0.1, 0.1*O54)), 1)</f>
         <v/>
       </c>
       <c r="U54" s="62">
-        <f>IF(T54&gt;0, RANK(T54, $T$31:$T$62), "-")</f>
+        <f>IF(T54&gt;70, RANK(T54, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V54" s="64">
-        <f>IF(W54="فاقد گزارش", "ثبت نشده", IF(T54&gt;=1, "عالی (۱۰۰٪+)", IF(T54&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T54&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T54&lt;=70, "ضعیف", IF(T54&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W54" s="64">
@@ -5343,15 +5346,15 @@
         <v/>
       </c>
       <c r="T55" s="83">
-        <f>AVERAGE(F55, I55, L55, O55, R55)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F55 + 0.3*I55) + MIN(0.5, 0.5*L55 + MAX(0, 0.1*F55 + 0.3*I55 - 0.4)) + MIN(0.1, 0.1*O55)), 1)</f>
         <v/>
       </c>
       <c r="U55" s="58">
-        <f>IF(T55&gt;0, RANK(T55, $T$31:$T$62), "-")</f>
+        <f>IF(T55&gt;70, RANK(T55, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V55" s="60">
-        <f>IF(W55="فاقد گزارش", "ثبت نشده", IF(T55&gt;=1, "عالی (۱۰۰٪+)", IF(T55&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T55&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T55&lt;=70, "ضعیف", IF(T55&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W55" s="60">
@@ -5437,15 +5440,15 @@
         <v/>
       </c>
       <c r="T56" s="86">
-        <f>AVERAGE(F56, I56, L56, O56, R56)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F56 + 0.3*I56) + MIN(0.5, 0.5*L56 + MAX(0, 0.1*F56 + 0.3*I56 - 0.4)) + MIN(0.1, 0.1*O56)), 1)</f>
         <v/>
       </c>
       <c r="U56" s="62">
-        <f>IF(T56&gt;0, RANK(T56, $T$31:$T$62), "-")</f>
+        <f>IF(T56&gt;70, RANK(T56, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V56" s="64">
-        <f>IF(W56="فاقد گزارش", "ثبت نشده", IF(T56&gt;=1, "عالی (۱۰۰٪+)", IF(T56&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T56&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T56&lt;=70, "ضعیف", IF(T56&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W56" s="64">
@@ -5531,15 +5534,15 @@
         <v/>
       </c>
       <c r="T57" s="83">
-        <f>AVERAGE(F57, I57, L57, O57, R57)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F57 + 0.3*I57) + MIN(0.5, 0.5*L57 + MAX(0, 0.1*F57 + 0.3*I57 - 0.4)) + MIN(0.1, 0.1*O57)), 1)</f>
         <v/>
       </c>
       <c r="U57" s="58">
-        <f>IF(T57&gt;0, RANK(T57, $T$31:$T$62), "-")</f>
+        <f>IF(T57&gt;70, RANK(T57, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V57" s="60">
-        <f>IF(W57="فاقد گزارش", "ثبت نشده", IF(T57&gt;=1, "عالی (۱۰۰٪+)", IF(T57&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T57&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T57&lt;=70, "ضعیف", IF(T57&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W57" s="60">
@@ -5625,15 +5628,15 @@
         <v/>
       </c>
       <c r="T58" s="86">
-        <f>AVERAGE(F58, I58, L58, O58, R58)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F58 + 0.3*I58) + MIN(0.5, 0.5*L58 + MAX(0, 0.1*F58 + 0.3*I58 - 0.4)) + MIN(0.1, 0.1*O58)), 1)</f>
         <v/>
       </c>
       <c r="U58" s="62">
-        <f>IF(T58&gt;0, RANK(T58, $T$31:$T$62), "-")</f>
+        <f>IF(T58&gt;70, RANK(T58, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V58" s="64">
-        <f>IF(W58="فاقد گزارش", "ثبت نشده", IF(T58&gt;=1, "عالی (۱۰۰٪+)", IF(T58&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T58&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T58&lt;=70, "ضعیف", IF(T58&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W58" s="64">
@@ -5719,15 +5722,15 @@
         <v/>
       </c>
       <c r="T59" s="83">
-        <f>AVERAGE(F59, I59, L59, O59, R59)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F59 + 0.3*I59) + MIN(0.5, 0.5*L59 + MAX(0, 0.1*F59 + 0.3*I59 - 0.4)) + MIN(0.1, 0.1*O59)), 1)</f>
         <v/>
       </c>
       <c r="U59" s="58">
-        <f>IF(T59&gt;0, RANK(T59, $T$31:$T$62), "-")</f>
+        <f>IF(T59&gt;70, RANK(T59, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V59" s="60">
-        <f>IF(W59="فاقد گزارش", "ثبت نشده", IF(T59&gt;=1, "عالی (۱۰۰٪+)", IF(T59&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T59&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T59&lt;=70, "ضعیف", IF(T59&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W59" s="60">
@@ -5813,15 +5816,15 @@
         <v/>
       </c>
       <c r="T60" s="86">
-        <f>AVERAGE(F60, I60, L60, O60, R60)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F60 + 0.3*I60) + MIN(0.5, 0.5*L60 + MAX(0, 0.1*F60 + 0.3*I60 - 0.4)) + MIN(0.1, 0.1*O60)), 1)</f>
         <v/>
       </c>
       <c r="U60" s="62">
-        <f>IF(T60&gt;0, RANK(T60, $T$31:$T$62), "-")</f>
+        <f>IF(T60&gt;70, RANK(T60, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V60" s="64">
-        <f>IF(W60="فاقد گزارش", "ثبت نشده", IF(T60&gt;=1, "عالی (۱۰۰٪+)", IF(T60&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T60&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T60&lt;=70, "ضعیف", IF(T60&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W60" s="64">
@@ -5907,15 +5910,15 @@
         <v/>
       </c>
       <c r="T61" s="83">
-        <f>AVERAGE(F61, I61, L61, O61, R61)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F61 + 0.3*I61) + MIN(0.5, 0.5*L61 + MAX(0, 0.1*F61 + 0.3*I61 - 0.4)) + MIN(0.1, 0.1*O61)), 1)</f>
         <v/>
       </c>
       <c r="U61" s="58">
-        <f>IF(T61&gt;0, RANK(T61, $T$31:$T$62), "-")</f>
+        <f>IF(T61&gt;70, RANK(T61, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V61" s="60">
-        <f>IF(W61="فاقد گزارش", "ثبت نشده", IF(T61&gt;=1, "عالی (۱۰۰٪+)", IF(T61&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T61&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T61&lt;=70, "ضعیف", IF(T61&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W61" s="60">
@@ -6001,15 +6004,15 @@
         <v/>
       </c>
       <c r="T62" s="86">
-        <f>AVERAGE(F62, I62, L62, O62, R62)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F62 + 0.3*I62) + MIN(0.5, 0.5*L62 + MAX(0, 0.1*F62 + 0.3*I62 - 0.4)) + MIN(0.1, 0.1*O62)), 1)</f>
         <v/>
       </c>
       <c r="U62" s="62">
-        <f>IF(T62&gt;0, RANK(T62, $T$31:$T$62), "-")</f>
+        <f>IF(T62&gt;70, RANK(T62, $T$31:$T$62), "-")</f>
         <v/>
       </c>
       <c r="V62" s="64">
-        <f>IF(W62="فاقد گزارش", "ثبت نشده", IF(T62&gt;=1, "عالی (۱۰۰٪+)", IF(T62&gt;=0.75, "خوب (۷۵-۹۹٪)", IF(T62&gt;=0.5, "متوسط (۵۰-۷۴٪)", "ضعیف (زیر ۵۰٪)"))))</f>
+        <f>IF(T62&lt;=70, "ضعیف", IF(T62&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
       <c r="W62" s="64">
@@ -6616,7 +6619,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="B1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="25.13" customWidth="1" style="12" min="2" max="5"/>
@@ -6654,7 +6657,7 @@
       </c>
       <c r="C3" s="135" t="inlineStr">
         <is>
-          <t>مرداد</t>
+          <t>شهریور</t>
         </is>
       </c>
       <c r="D3" s="134" t="inlineStr">
@@ -6794,11 +6797,11 @@
     <row r="11">
       <c r="B11" s="110" t="inlineStr">
         <is>
-          <t>نمره کل عملکرد:</t>
+          <t>نمره کل عملکرد (۷۰ تا ۱۰۰):</t>
         </is>
       </c>
       <c r="C11" s="111">
-        <f>AVERAGE(E5:E9)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*E5 + 0.3*E6) + MIN(0.5, 0.5*E7 + MAX(0, 0.1*E5 + 0.3*E6 - 0.4)) + MIN(0.1, 0.1*E8)), 1)</f>
         <v/>
       </c>
       <c r="D11" s="6" t="n"/>
@@ -6820,33 +6823,44 @@
     <row r="13" ht="22" customHeight="1" s="12">
       <c r="B13" s="112" t="inlineStr">
         <is>
-          <t>سطح ارزیابی عملکرد:</t>
+          <t>سطح ارزیابی (۳ سطح):</t>
         </is>
       </c>
       <c r="C13" s="113">
-        <f>IFERROR(VLOOKUP($C$2, 'داشبورد مانیتورینگ نواحی'!$B$31:$V$62, 21, FALSE), "-")</f>
+        <f>IF(C11&lt;=70, "ضعیف", IF(C11&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" s="12">
       <c r="B14" s="112" t="inlineStr">
         <is>
-          <t>تعداد حوزه مقاومت:</t>
-        </is>
-      </c>
-      <c r="C14" s="114">
-        <f>IFERROR(VLOOKUP($C$2, 'پایگاه داده حد انتظار'!$A$2:$B$33, 2, FALSE), 0)</f>
+          <t>درصد تحقق وزنی اهداف:</t>
+        </is>
+      </c>
+      <c r="C14" s="140">
+        <f>(MIN(0.4, 0.1*E5 + 0.3*E6) + MIN(0.5, 0.5*E7 + MAX(0, 0.1*E5 + 0.3*E6 - 0.4)) + MIN(0.1, 0.1*E8))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" s="12">
       <c r="B15" s="112" t="inlineStr">
         <is>
+          <t>تعداد حوزه مقاومت:</t>
+        </is>
+      </c>
+      <c r="C15" s="114">
+        <f>IFERROR(VLOOKUP(, 'پایگاه داده حد انتظار'!:3, 2, FALSE), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="0" t="inlineStr">
+        <is>
           <t>حدانتظار اعضای انجمن:</t>
         </is>
       </c>
-      <c r="C15" s="114">
-        <f>IFERROR(VLOOKUP($C$2, 'پایگاه داده حد انتظار'!$A$2:$H$33, 8, FALSE), 0)</f>
+      <c r="C16" s="0">
+        <f>IFERROR(VLOOKUP(, 'پایگاه داده حد انتظار'!:3, 8, FALSE), 0)</f>
         <v/>
       </c>
     </row>
@@ -6928,11 +6942,21 @@
           <t>آران و بیدگل</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="9" t="n"/>
+      <c r="B2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
@@ -6940,11 +6964,21 @@
           <t>امام حسین(ع)</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="9" t="n"/>
-      <c r="F3" s="9" t="n"/>
+      <c r="B3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
@@ -6953,7 +6987,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>1064</v>
+        <v>0</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>0</v>
@@ -6965,7 +6999,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -6975,7 +7009,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>4189</v>
+        <v>0</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>0</v>
@@ -6984,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -6997,7 +7031,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>0</v>
@@ -7006,10 +7040,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -7019,19 +7053,19 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -7044,7 +7078,7 @@
         <v>46</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>4396</v>
@@ -7062,11 +7096,21 @@
           <t>بویین و میاندشت</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
+      <c r="B9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -7074,11 +7118,21 @@
           <t>تیران و کرون</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
+      <c r="B10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -7087,7 +7141,7 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>0</v>
@@ -7099,7 +7153,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -7108,11 +7162,21 @@
           <t>چادگان</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n"/>
+      <c r="B12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -7120,11 +7184,21 @@
           <t>خمینی شهر</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
+      <c r="B13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -7133,19 +7207,19 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>1634</v>
+        <v>0</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -7154,11 +7228,21 @@
           <t>خور و بیابانک</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
+      <c r="B15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
@@ -7170,13 +7254,13 @@
         <v>2299</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>1</v>
@@ -7188,11 +7272,21 @@
           <t>دهاقان</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
+      <c r="B17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
@@ -7200,11 +7294,21 @@
           <t>سمیرم</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="9" t="n"/>
+      <c r="B18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -7212,11 +7316,21 @@
           <t>شاهین شهر</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="9" t="n"/>
+      <c r="B19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -7225,19 +7339,19 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>3366</v>
+        <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -7246,11 +7360,21 @@
           <t>فریدن</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
+      <c r="B21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
@@ -7268,10 +7392,10 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -7281,19 +7405,19 @@
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>1583</v>
+        <v>0</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>11348</v>
+        <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -7303,19 +7427,19 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -7325,19 +7449,19 @@
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>502</v>
+        <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -7346,11 +7470,21 @@
           <t>گلپایگان</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n"/>
+      <c r="B26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
@@ -7359,7 +7493,7 @@
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>0</v>
@@ -7371,7 +7505,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -7380,11 +7514,21 @@
           <t>مبارکه</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="9" t="n"/>
+      <c r="B28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
@@ -7392,11 +7536,21 @@
           <t>نایین</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="9" t="n"/>
+      <c r="B29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
@@ -7404,11 +7558,21 @@
           <t>نجف آباد</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
+      <c r="B30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
@@ -7417,19 +7581,19 @@
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>1002</v>
+        <v>0</v>
       </c>
       <c r="C31" s="9" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>3800</v>
+        <v>0</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -7438,11 +7602,21 @@
           <t>ورزنه</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="9" t="n"/>
+      <c r="B32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
@@ -7450,11 +7624,21 @@
           <t>هرند</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
+      <c r="B33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/تهیه کارنامه نواحی.xlsx
+++ b/تهیه کارنامه نواحی.xlsx
@@ -6619,7 +6619,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="25.13" customWidth="1" style="12" min="2" max="5"/>
@@ -7078,7 +7078,7 @@
         <v>46</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>4396</v>
@@ -7251,16 +7251,16 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>2299</v>
+        <v>4552</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>1</v>
@@ -7471,19 +7471,19 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C26" s="9" t="n">
-        <v>0</v>
+        <v>2170</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0</v>
+        <v>620</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">

--- a/تهیه کارنامه نواحی.xlsx
+++ b/تهیه کارنامه نواحی.xlsx
@@ -6657,7 +6657,7 @@
       </c>
       <c r="C3" s="135" t="inlineStr">
         <is>
-          <t>شهریور</t>
+          <t>تیر</t>
         </is>
       </c>
       <c r="D3" s="134" t="inlineStr">
@@ -7075,19 +7075,19 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>4396</v>
+        <v>0</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>4552</v>
+        <v>0</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>0</v>
@@ -7263,7 +7263,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -7471,16 +7471,16 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2170</v>
+        <v>500</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>620</v>
+        <v>400</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>1</v>
